--- a/diseases/d128/2010-2014.xlsx
+++ b/diseases/d128/2010-2014.xlsx
@@ -4613,9 +4613,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5057,9 +5054,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5501,9 +5495,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -5945,9 +5936,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6389,9 +6377,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -6833,9 +6818,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7277,9 +7259,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7721,9 +7700,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8165,9 +8141,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8609,9 +8582,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9053,9 +9023,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9464,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9941,9 +9905,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10346,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10787,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11228,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11717,9 +11669,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12161,9 +12110,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12605,9 +12551,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13049,9 +12992,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13493,9 +13433,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -14381,9 +14318,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15351,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16601,9 +16532,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17785,9 +17713,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18181,9 +18106,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -19365,9 +19287,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20401,9 +20320,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21437,9 +21353,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -22473,9 +22386,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -23657,9 +23567,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24693,9 +24600,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25729,9 +25633,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26913,9 +26814,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -27949,9 +27847,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -29133,9 +29028,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -30169,9 +30061,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -31353,9 +31242,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -31749,9 +31635,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -32933,9 +32816,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -33969,9 +33849,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -35005,9 +34882,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -36041,9 +35915,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -37225,9 +37096,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -38261,9 +38129,6 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
@@ -39445,9 +39310,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -40481,9 +40343,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -41517,9 +41376,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -42701,9 +42557,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -43735,9 +43588,6 @@
         <v>0</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
